--- a/backend/data/financials_by_company/1823.HK.xlsx
+++ b/backend/data/financials_by_company/1823.HK.xlsx
@@ -662,204 +662,202 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>163500</v>
+        <v>-53681.127729</v>
       </c>
       <c r="C2" t="n">
-        <v>0.25</v>
+        <v>0.335507</v>
       </c>
       <c r="D2" t="n">
-        <v>35115000</v>
+        <v>194906000</v>
       </c>
       <c r="E2" t="n">
-        <v>654000</v>
+        <v>-160000</v>
       </c>
       <c r="F2" t="n">
-        <v>654000</v>
+        <v>-160000</v>
       </c>
       <c r="G2" t="n">
-        <v>-8514000</v>
+        <v>37207000</v>
       </c>
       <c r="H2" t="n">
-        <v>39888000</v>
+        <v>64025000</v>
       </c>
       <c r="I2" t="n">
-        <v>158641000</v>
+        <v>480024000</v>
       </c>
       <c r="J2" t="n">
-        <v>35769000</v>
+        <v>194746000</v>
       </c>
       <c r="K2" t="n">
-        <v>-4119000</v>
+        <v>130721000</v>
       </c>
       <c r="L2" t="n">
-        <v>-3158000</v>
+        <v>159000</v>
       </c>
       <c r="M2" t="n">
-        <v>5102000</v>
+        <v>2676000</v>
       </c>
       <c r="N2" t="n">
-        <v>1944000</v>
+        <v>2835000</v>
       </c>
       <c r="O2" t="n">
-        <v>-9004500</v>
+        <v>37313318.872271</v>
       </c>
       <c r="P2" t="n">
-        <v>-8514000</v>
+        <v>86426000</v>
       </c>
       <c r="Q2" t="n">
-        <v>216338000</v>
+        <v>578192000</v>
       </c>
       <c r="R2" t="n">
-        <v>-16645000</v>
+        <v>116549000</v>
       </c>
       <c r="S2" t="n">
-        <v>412608000</v>
+        <v>412664000</v>
       </c>
       <c r="T2" t="n">
         <v>412608000</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0206</v>
+        <v>0.2095</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.0206</v>
+        <v>0.2095</v>
       </c>
       <c r="W2" t="n">
-        <v>-8514000</v>
+        <v>86426000</v>
       </c>
       <c r="X2" t="n">
-        <v>-8514000</v>
+        <v>86426000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-8514000</v>
+        <v>86426000</v>
       </c>
       <c r="AA2" t="n">
-        <v>4771000</v>
+        <v>-47878000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-13285000</v>
+        <v>134304000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>49219000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-13285000</v>
+        <v>85085000</v>
       </c>
       <c r="AE2" t="n">
-        <v>4064000</v>
+        <v>42960000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-9221000</v>
+        <v>128045000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1665000</v>
+        <v>1592000</v>
       </c>
       <c r="AH2" t="n">
-        <v>654000</v>
+        <v>-160000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-415000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-239000</v>
-      </c>
+        <v>160000</v>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="n">
-        <v>-3158000</v>
+        <v>159000</v>
       </c>
       <c r="AL2" t="n">
-        <v>5102000</v>
+        <v>2676000</v>
       </c>
       <c r="AM2" t="n">
-        <v>1944000</v>
+        <v>2835000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-18193000</v>
+        <v>110260000</v>
       </c>
       <c r="AO2" t="n">
-        <v>57697000</v>
+        <v>98168000</v>
       </c>
       <c r="AP2" t="n">
-        <v>57697000</v>
+        <v>98168000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10481000</v>
+        <v>25801000</v>
       </c>
       <c r="AR2" t="n">
-        <v>47216000</v>
+        <v>72367000</v>
       </c>
       <c r="AS2" t="n">
-        <v>39504000</v>
+        <v>208428000</v>
       </c>
       <c r="AT2" t="n">
-        <v>158641000</v>
+        <v>480024000</v>
       </c>
       <c r="AU2" t="n">
-        <v>198145000</v>
+        <v>688452000</v>
       </c>
       <c r="AV2" t="n">
-        <v>198145000</v>
+        <v>688452000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-906750</v>
+        <v>-121704.975473</v>
       </c>
       <c r="C3" t="n">
-        <v>0.25</v>
+        <v>0.281724</v>
       </c>
       <c r="D3" t="n">
-        <v>83555000</v>
+        <v>134527000</v>
       </c>
       <c r="E3" t="n">
-        <v>-3627000</v>
+        <v>-432000</v>
       </c>
       <c r="F3" t="n">
-        <v>-3627000</v>
+        <v>-432000</v>
       </c>
       <c r="G3" t="n">
-        <v>-12968000</v>
+        <v>11313000</v>
       </c>
       <c r="H3" t="n">
-        <v>38972000</v>
+        <v>64066000</v>
       </c>
       <c r="I3" t="n">
-        <v>292090000</v>
+        <v>290201000</v>
       </c>
       <c r="J3" t="n">
-        <v>79928000</v>
+        <v>134095000</v>
       </c>
       <c r="K3" t="n">
-        <v>40956000</v>
+        <v>70029000</v>
       </c>
       <c r="L3" t="n">
-        <v>979000</v>
+        <v>483000</v>
       </c>
       <c r="M3" t="n">
-        <v>1864000</v>
+        <v>1533000</v>
       </c>
       <c r="N3" t="n">
-        <v>2843000</v>
+        <v>2016000</v>
       </c>
       <c r="O3" t="n">
-        <v>-10247750</v>
+        <v>11623295.024527</v>
       </c>
       <c r="P3" t="n">
-        <v>329432000</v>
+        <v>49028000</v>
       </c>
       <c r="Q3" t="n">
-        <v>366370000</v>
+        <v>344740000</v>
       </c>
       <c r="R3" t="n">
-        <v>40730000</v>
+        <v>65826000</v>
       </c>
       <c r="S3" t="n">
         <v>412608000</v>
@@ -868,144 +866,144 @@
         <v>412608000</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7984</v>
+        <v>0.1188</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7984</v>
+        <v>0.1188</v>
       </c>
       <c r="W3" t="n">
-        <v>329432000</v>
+        <v>49028000</v>
       </c>
       <c r="X3" t="n">
-        <v>329432000</v>
+        <v>49028000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>329432000</v>
+        <v>49028000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-29906000</v>
+        <v>-37886000</v>
       </c>
       <c r="AB3" t="n">
-        <v>359338000</v>
+        <v>86914000</v>
       </c>
       <c r="AC3" t="n">
-        <v>342400000</v>
+        <v>37715000</v>
       </c>
       <c r="AD3" t="n">
-        <v>16938000</v>
+        <v>49199000</v>
       </c>
       <c r="AE3" t="n">
-        <v>22154000</v>
+        <v>19297000</v>
       </c>
       <c r="AF3" t="n">
-        <v>39092000</v>
+        <v>68496000</v>
       </c>
       <c r="AG3" t="n">
-        <v>1360000</v>
+        <v>2986000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-3627000</v>
+        <v>-432000</v>
       </c>
       <c r="AI3" t="n">
-        <v>23000</v>
+        <v>432000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3604000</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>979000</v>
+        <v>483000</v>
       </c>
       <c r="AL3" t="n">
-        <v>1864000</v>
+        <v>1533000</v>
       </c>
       <c r="AM3" t="n">
-        <v>2843000</v>
+        <v>2016000</v>
       </c>
       <c r="AN3" t="n">
-        <v>40734000</v>
+        <v>65146000</v>
       </c>
       <c r="AO3" t="n">
-        <v>74280000</v>
+        <v>54539000</v>
       </c>
       <c r="AP3" t="n">
-        <v>74280000</v>
+        <v>54539000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15377000</v>
+        <v>15872000</v>
       </c>
       <c r="AR3" t="n">
-        <v>58903000</v>
+        <v>38667000</v>
       </c>
       <c r="AS3" t="n">
-        <v>115014000</v>
+        <v>119685000</v>
       </c>
       <c r="AT3" t="n">
-        <v>292090000</v>
+        <v>290201000</v>
       </c>
       <c r="AU3" t="n">
-        <v>407104000</v>
+        <v>409886000</v>
       </c>
       <c r="AV3" t="n">
-        <v>407104000</v>
+        <v>409886000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-121704.975473</v>
+        <v>-906750</v>
       </c>
       <c r="C4" t="n">
-        <v>0.281724</v>
+        <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>134527000</v>
+        <v>83555000</v>
       </c>
       <c r="E4" t="n">
-        <v>-432000</v>
+        <v>-3627000</v>
       </c>
       <c r="F4" t="n">
-        <v>-432000</v>
+        <v>-3627000</v>
       </c>
       <c r="G4" t="n">
-        <v>11313000</v>
+        <v>-12968000</v>
       </c>
       <c r="H4" t="n">
-        <v>64066000</v>
+        <v>38972000</v>
       </c>
       <c r="I4" t="n">
-        <v>290201000</v>
+        <v>292090000</v>
       </c>
       <c r="J4" t="n">
-        <v>134095000</v>
+        <v>79928000</v>
       </c>
       <c r="K4" t="n">
-        <v>70029000</v>
+        <v>40956000</v>
       </c>
       <c r="L4" t="n">
-        <v>483000</v>
+        <v>979000</v>
       </c>
       <c r="M4" t="n">
-        <v>1533000</v>
+        <v>1864000</v>
       </c>
       <c r="N4" t="n">
-        <v>2016000</v>
+        <v>2843000</v>
       </c>
       <c r="O4" t="n">
-        <v>11623295.024527</v>
+        <v>-10247750</v>
       </c>
       <c r="P4" t="n">
-        <v>49028000</v>
+        <v>329432000</v>
       </c>
       <c r="Q4" t="n">
-        <v>344740000</v>
+        <v>366370000</v>
       </c>
       <c r="R4" t="n">
-        <v>65826000</v>
+        <v>40730000</v>
       </c>
       <c r="S4" t="n">
         <v>412608000</v>
@@ -1014,232 +1012,234 @@
         <v>412608000</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1188</v>
+        <v>0.7984</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1188</v>
+        <v>0.7984</v>
       </c>
       <c r="W4" t="n">
-        <v>49028000</v>
+        <v>329432000</v>
       </c>
       <c r="X4" t="n">
-        <v>49028000</v>
+        <v>329432000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>49028000</v>
+        <v>329432000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-37886000</v>
+        <v>-29906000</v>
       </c>
       <c r="AB4" t="n">
-        <v>86914000</v>
+        <v>359338000</v>
       </c>
       <c r="AC4" t="n">
-        <v>37715000</v>
+        <v>342400000</v>
       </c>
       <c r="AD4" t="n">
-        <v>49199000</v>
+        <v>16938000</v>
       </c>
       <c r="AE4" t="n">
-        <v>19297000</v>
+        <v>22154000</v>
       </c>
       <c r="AF4" t="n">
-        <v>68496000</v>
+        <v>39092000</v>
       </c>
       <c r="AG4" t="n">
-        <v>2986000</v>
+        <v>1360000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-432000</v>
+        <v>-3627000</v>
       </c>
       <c r="AI4" t="n">
-        <v>432000</v>
+        <v>23000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>3604000</v>
       </c>
       <c r="AK4" t="n">
-        <v>483000</v>
+        <v>979000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1533000</v>
+        <v>1864000</v>
       </c>
       <c r="AM4" t="n">
-        <v>2016000</v>
+        <v>2843000</v>
       </c>
       <c r="AN4" t="n">
-        <v>65146000</v>
+        <v>40734000</v>
       </c>
       <c r="AO4" t="n">
-        <v>54539000</v>
+        <v>74280000</v>
       </c>
       <c r="AP4" t="n">
-        <v>54539000</v>
+        <v>74280000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15872000</v>
+        <v>15377000</v>
       </c>
       <c r="AR4" t="n">
-        <v>38667000</v>
+        <v>58903000</v>
       </c>
       <c r="AS4" t="n">
-        <v>119685000</v>
+        <v>115014000</v>
       </c>
       <c r="AT4" t="n">
-        <v>290201000</v>
+        <v>292090000</v>
       </c>
       <c r="AU4" t="n">
-        <v>409886000</v>
+        <v>407104000</v>
       </c>
       <c r="AV4" t="n">
-        <v>409886000</v>
+        <v>407104000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-53681.127729</v>
+        <v>163500</v>
       </c>
       <c r="C5" t="n">
-        <v>0.335507</v>
+        <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>194906000</v>
+        <v>35115000</v>
       </c>
       <c r="E5" t="n">
-        <v>-160000</v>
+        <v>654000</v>
       </c>
       <c r="F5" t="n">
-        <v>-160000</v>
+        <v>654000</v>
       </c>
       <c r="G5" t="n">
-        <v>37207000</v>
+        <v>-8514000</v>
       </c>
       <c r="H5" t="n">
-        <v>64025000</v>
+        <v>39888000</v>
       </c>
       <c r="I5" t="n">
-        <v>480024000</v>
+        <v>158641000</v>
       </c>
       <c r="J5" t="n">
-        <v>194746000</v>
+        <v>35769000</v>
       </c>
       <c r="K5" t="n">
-        <v>130721000</v>
+        <v>-4119000</v>
       </c>
       <c r="L5" t="n">
-        <v>159000</v>
+        <v>-3158000</v>
       </c>
       <c r="M5" t="n">
-        <v>2676000</v>
+        <v>5102000</v>
       </c>
       <c r="N5" t="n">
-        <v>2835000</v>
+        <v>1944000</v>
       </c>
       <c r="O5" t="n">
-        <v>37313318.872271</v>
+        <v>-9004500</v>
       </c>
       <c r="P5" t="n">
-        <v>86426000</v>
+        <v>-8514000</v>
       </c>
       <c r="Q5" t="n">
-        <v>578192000</v>
+        <v>216338000</v>
       </c>
       <c r="R5" t="n">
-        <v>116549000</v>
+        <v>-16645000</v>
       </c>
       <c r="S5" t="n">
-        <v>412664000</v>
+        <v>412608000</v>
       </c>
       <c r="T5" t="n">
         <v>412608000</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2095</v>
+        <v>-0.0206</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2095</v>
+        <v>-0.0206</v>
       </c>
       <c r="W5" t="n">
-        <v>86426000</v>
+        <v>-8514000</v>
       </c>
       <c r="X5" t="n">
-        <v>86426000</v>
+        <v>-8514000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>86426000</v>
+        <v>-8514000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-47878000</v>
+        <v>4771000</v>
       </c>
       <c r="AB5" t="n">
-        <v>134304000</v>
+        <v>-13285000</v>
       </c>
       <c r="AC5" t="n">
-        <v>49219000</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>85085000</v>
+        <v>-13285000</v>
       </c>
       <c r="AE5" t="n">
-        <v>42960000</v>
+        <v>4064000</v>
       </c>
       <c r="AF5" t="n">
-        <v>128045000</v>
+        <v>-9221000</v>
       </c>
       <c r="AG5" t="n">
-        <v>1592000</v>
+        <v>1665000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-160000</v>
+        <v>654000</v>
       </c>
       <c r="AI5" t="n">
-        <v>160000</v>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
+        <v>-415000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-239000</v>
+      </c>
       <c r="AK5" t="n">
-        <v>159000</v>
+        <v>-3158000</v>
       </c>
       <c r="AL5" t="n">
-        <v>2676000</v>
+        <v>5102000</v>
       </c>
       <c r="AM5" t="n">
-        <v>2835000</v>
+        <v>1944000</v>
       </c>
       <c r="AN5" t="n">
-        <v>110260000</v>
+        <v>-18193000</v>
       </c>
       <c r="AO5" t="n">
-        <v>98168000</v>
+        <v>57697000</v>
       </c>
       <c r="AP5" t="n">
-        <v>98168000</v>
+        <v>57697000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>25801000</v>
+        <v>10481000</v>
       </c>
       <c r="AR5" t="n">
-        <v>72367000</v>
+        <v>47216000</v>
       </c>
       <c r="AS5" t="n">
-        <v>208428000</v>
+        <v>39504000</v>
       </c>
       <c r="AT5" t="n">
-        <v>480024000</v>
+        <v>158641000</v>
       </c>
       <c r="AU5" t="n">
-        <v>688452000</v>
+        <v>198145000</v>
       </c>
       <c r="AV5" t="n">
-        <v>688452000</v>
+        <v>198145000</v>
       </c>
     </row>
   </sheetData>
@@ -1580,7 +1580,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>412608000</v>
@@ -1589,46 +1589,46 @@
         <v>412608000</v>
       </c>
       <c r="D2" t="n">
-        <v>58837000</v>
+        <v>716013000</v>
       </c>
       <c r="E2" t="n">
-        <v>247521000</v>
+        <v>990905000</v>
       </c>
       <c r="F2" t="n">
-        <v>524784000</v>
+        <v>-730951000</v>
       </c>
       <c r="G2" t="n">
-        <v>995738000</v>
+        <v>1459511000</v>
       </c>
       <c r="H2" t="n">
-        <v>479274000</v>
+        <v>300621000</v>
       </c>
       <c r="I2" t="n">
-        <v>524784000</v>
+        <v>-730951000</v>
       </c>
       <c r="J2" t="n">
-        <v>2928000</v>
+        <v>2981000</v>
       </c>
       <c r="K2" t="n">
-        <v>751145000</v>
+        <v>471587000</v>
       </c>
       <c r="L2" t="n">
-        <v>850614000</v>
+        <v>1349511000</v>
       </c>
       <c r="M2" t="n">
-        <v>1078429000</v>
+        <v>718076000</v>
       </c>
       <c r="N2" t="n">
-        <v>327284000</v>
+        <v>246489000</v>
       </c>
       <c r="O2" t="n">
-        <v>751145000</v>
+        <v>471587000</v>
       </c>
       <c r="P2" t="n">
-        <v>5085000</v>
+        <v>32857000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-18214000</v>
+        <v>-302889000</v>
       </c>
       <c r="R2" t="n">
         <v>51487000</v>
@@ -1640,128 +1640,134 @@
         <v>3634000</v>
       </c>
       <c r="U2" t="n">
-        <v>334380000</v>
+        <v>1189941000</v>
       </c>
       <c r="V2" t="n">
-        <v>100009000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
+        <v>962812000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>83375000</v>
+      </c>
       <c r="X2" t="n">
-        <v>100009000</v>
+        <v>879437000</v>
       </c>
       <c r="Y2" t="n">
-        <v>540000</v>
+        <v>1513000</v>
       </c>
       <c r="Z2" t="n">
-        <v>99469000</v>
+        <v>877924000</v>
       </c>
       <c r="AA2" t="n">
-        <v>234371000</v>
+        <v>227129000</v>
       </c>
       <c r="AB2" t="n">
-        <v>147512000</v>
+        <v>111468000</v>
       </c>
       <c r="AC2" t="n">
-        <v>2388000</v>
+        <v>1468000</v>
       </c>
       <c r="AD2" t="n">
-        <v>145124000</v>
+        <v>110000000</v>
       </c>
       <c r="AE2" t="n">
-        <v>74251000</v>
+        <v>81338000</v>
       </c>
       <c r="AF2" t="n">
-        <v>18739000</v>
+        <v>23947000</v>
       </c>
       <c r="AG2" t="n">
-        <v>6381000</v>
+        <v>15235000</v>
       </c>
       <c r="AH2" t="n">
-        <v>49131000</v>
+        <v>42156000</v>
       </c>
       <c r="AI2" t="n">
-        <v>1412809000</v>
+        <v>1908017000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>699164000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+        <v>1380267000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-67196458.196013</v>
+      </c>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
-        <v>266000</v>
+        <v>114015000</v>
       </c>
       <c r="AN2" t="n">
-        <v>163579000</v>
+        <v>34065000</v>
       </c>
       <c r="AO2" t="n">
-        <v>163579000</v>
+        <v>34065000</v>
       </c>
       <c r="AP2" t="n">
-        <v>226361000</v>
+        <v>1202538000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>226361000</v>
+        <v>1202538000</v>
       </c>
       <c r="AR2" t="n">
-        <v>288310000</v>
+        <v>29649000</v>
       </c>
       <c r="AS2" t="n">
-        <v>-11012000</v>
+        <v>-36896000</v>
       </c>
       <c r="AT2" t="n">
-        <v>299322000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>279075000</v>
-      </c>
+        <v>66545000</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="n">
-        <v>11250000</v>
+        <v>55616000</v>
       </c>
       <c r="AW2" t="n">
-        <v>8997000</v>
-      </c>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
+        <v>10929000</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>6582000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
       <c r="AZ2" t="n">
-        <v>713645000</v>
-      </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
+        <v>527750000</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1342000</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0</v>
+      </c>
       <c r="BC2" t="n">
-        <v>48145000</v>
+        <v>114375000</v>
       </c>
       <c r="BD2" t="n">
-        <v>390608000</v>
+        <v>81763000</v>
       </c>
       <c r="BE2" t="n">
-        <v>383541000</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>7067000</v>
-      </c>
+        <v>81763000</v>
+      </c>
+      <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="n">
-        <v>43664000</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>40632000</v>
-      </c>
+        <v>52290000</v>
+      </c>
+      <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="n">
-        <v>4840000</v>
+        <v>6069000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>185756000</v>
+        <v>271911000</v>
       </c>
       <c r="BK2" t="inlineStr"/>
       <c r="BL2" t="n">
-        <v>185756000</v>
+        <v>271911000</v>
       </c>
       <c r="BM2" t="n">
-        <v>185756000</v>
+        <v>271911000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>412608000</v>
@@ -1771,43 +1777,43 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>1459000</v>
+        <v>51650000</v>
       </c>
       <c r="F3" t="n">
-        <v>547535000</v>
+        <v>403077000</v>
       </c>
       <c r="G3" t="n">
-        <v>803826000</v>
+        <v>568168000</v>
       </c>
       <c r="H3" t="n">
-        <v>595365000</v>
+        <v>553843000</v>
       </c>
       <c r="I3" t="n">
-        <v>547535000</v>
+        <v>403077000</v>
       </c>
       <c r="J3" t="n">
-        <v>1459000</v>
+        <v>1650000</v>
       </c>
       <c r="K3" t="n">
-        <v>803826000</v>
+        <v>518168000</v>
       </c>
       <c r="L3" t="n">
-        <v>803826000</v>
+        <v>518168000</v>
       </c>
       <c r="M3" t="n">
-        <v>1124022000</v>
+        <v>803030000</v>
       </c>
       <c r="N3" t="n">
-        <v>320196000</v>
+        <v>284862000</v>
       </c>
       <c r="O3" t="n">
-        <v>803826000</v>
+        <v>518168000</v>
       </c>
       <c r="P3" t="n">
         <v>5085000</v>
       </c>
       <c r="Q3" t="n">
-        <v>35889000</v>
+        <v>-229664000</v>
       </c>
       <c r="R3" t="n">
         <v>51487000</v>
@@ -1819,140 +1825,142 @@
         <v>3634000</v>
       </c>
       <c r="U3" t="n">
-        <v>125208000</v>
+        <v>1152922000</v>
       </c>
       <c r="V3" t="n">
-        <v>560000</v>
+        <v>263000</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>560000</v>
+        <v>263000</v>
       </c>
       <c r="Y3" t="n">
-        <v>560000</v>
+        <v>263000</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>124648000</v>
+        <v>1152659000</v>
       </c>
       <c r="AB3" t="n">
-        <v>899000</v>
+        <v>51387000</v>
       </c>
       <c r="AC3" t="n">
-        <v>899000</v>
+        <v>1387000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>50000000</v>
       </c>
       <c r="AE3" t="n">
-        <v>46195000</v>
+        <v>114310000</v>
       </c>
       <c r="AF3" t="n">
-        <v>18477000</v>
+        <v>113159000</v>
       </c>
       <c r="AG3" t="n">
-        <v>14790000</v>
+        <v>3158000</v>
       </c>
       <c r="AH3" t="n">
-        <v>4730000</v>
+        <v>5537000</v>
       </c>
       <c r="AI3" t="n">
-        <v>1249230000</v>
+        <v>1955952000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>529217000</v>
+        <v>249450000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-211164000</v>
+        <v>-7094000</v>
       </c>
       <c r="AL3" t="n">
-        <v>37120000</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>162000</v>
+        <v>1382000</v>
       </c>
       <c r="AN3" t="n">
-        <v>180563000</v>
+        <v>125883000</v>
       </c>
       <c r="AO3" t="n">
-        <v>180563000</v>
+        <v>125883000</v>
       </c>
       <c r="AP3" t="n">
-        <v>256291000</v>
+        <v>115091000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>256291000</v>
+        <v>115091000</v>
       </c>
       <c r="AR3" t="n">
-        <v>72190000</v>
+        <v>7094000</v>
       </c>
       <c r="AS3" t="n">
-        <v>-12566000</v>
+        <v>-10514000</v>
       </c>
       <c r="AT3" t="n">
-        <v>84756000</v>
+        <v>17608000</v>
       </c>
       <c r="AU3" t="n">
-        <v>63533000</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>13121000</v>
+        <v>10488000</v>
       </c>
       <c r="AW3" t="n">
-        <v>8102000</v>
+        <v>7120000</v>
       </c>
       <c r="AX3" t="n">
-        <v>7530000</v>
+        <v>6756000</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>720013000</v>
-      </c>
-      <c r="BA3" t="inlineStr"/>
+        <v>1706502000</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>12261000</v>
+      </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1251957000</v>
       </c>
       <c r="BC3" t="n">
-        <v>23273000</v>
+        <v>47886000</v>
       </c>
       <c r="BD3" t="n">
-        <v>256628000</v>
+        <v>159933000</v>
       </c>
       <c r="BE3" t="n">
-        <v>245455000</v>
+        <v>159933000</v>
       </c>
       <c r="BF3" t="n">
-        <v>11173000</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>98566000</v>
+        <v>27799000</v>
       </c>
       <c r="BH3" t="n">
-        <v>11281000</v>
+        <v>1249000</v>
       </c>
       <c r="BI3" t="n">
-        <v>2303000</v>
+        <v>1007000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>327962000</v>
+        <v>216671000</v>
       </c>
       <c r="BK3" t="n">
-        <v>14242000</v>
+        <v>11012000</v>
       </c>
       <c r="BL3" t="n">
-        <v>313720000</v>
+        <v>205659000</v>
       </c>
       <c r="BM3" t="n">
-        <v>313720000</v>
+        <v>205659000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>412608000</v>
@@ -1962,43 +1970,43 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>51650000</v>
+        <v>1459000</v>
       </c>
       <c r="F4" t="n">
-        <v>403077000</v>
+        <v>547535000</v>
       </c>
       <c r="G4" t="n">
-        <v>568168000</v>
+        <v>803826000</v>
       </c>
       <c r="H4" t="n">
-        <v>553843000</v>
+        <v>595365000</v>
       </c>
       <c r="I4" t="n">
-        <v>403077000</v>
+        <v>547535000</v>
       </c>
       <c r="J4" t="n">
-        <v>1650000</v>
+        <v>1459000</v>
       </c>
       <c r="K4" t="n">
-        <v>518168000</v>
+        <v>803826000</v>
       </c>
       <c r="L4" t="n">
-        <v>518168000</v>
+        <v>803826000</v>
       </c>
       <c r="M4" t="n">
-        <v>803030000</v>
+        <v>1124022000</v>
       </c>
       <c r="N4" t="n">
-        <v>284862000</v>
+        <v>320196000</v>
       </c>
       <c r="O4" t="n">
-        <v>518168000</v>
+        <v>803826000</v>
       </c>
       <c r="P4" t="n">
         <v>5085000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-229664000</v>
+        <v>35889000</v>
       </c>
       <c r="R4" t="n">
         <v>51487000</v>
@@ -2010,142 +2018,140 @@
         <v>3634000</v>
       </c>
       <c r="U4" t="n">
-        <v>1152922000</v>
+        <v>125208000</v>
       </c>
       <c r="V4" t="n">
-        <v>263000</v>
+        <v>560000</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>263000</v>
+        <v>560000</v>
       </c>
       <c r="Y4" t="n">
-        <v>263000</v>
+        <v>560000</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1152659000</v>
+        <v>124648000</v>
       </c>
       <c r="AB4" t="n">
-        <v>51387000</v>
+        <v>899000</v>
       </c>
       <c r="AC4" t="n">
-        <v>1387000</v>
+        <v>899000</v>
       </c>
       <c r="AD4" t="n">
-        <v>50000000</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>114310000</v>
+        <v>46195000</v>
       </c>
       <c r="AF4" t="n">
-        <v>113159000</v>
+        <v>18477000</v>
       </c>
       <c r="AG4" t="n">
-        <v>3158000</v>
+        <v>14790000</v>
       </c>
       <c r="AH4" t="n">
-        <v>5537000</v>
+        <v>4730000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1955952000</v>
+        <v>1249230000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>249450000</v>
+        <v>529217000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-7094000</v>
+        <v>-211164000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>37120000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1382000</v>
+        <v>162000</v>
       </c>
       <c r="AN4" t="n">
-        <v>125883000</v>
+        <v>180563000</v>
       </c>
       <c r="AO4" t="n">
-        <v>125883000</v>
+        <v>180563000</v>
       </c>
       <c r="AP4" t="n">
-        <v>115091000</v>
+        <v>256291000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>115091000</v>
+        <v>256291000</v>
       </c>
       <c r="AR4" t="n">
-        <v>7094000</v>
+        <v>72190000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-10514000</v>
+        <v>-12566000</v>
       </c>
       <c r="AT4" t="n">
-        <v>17608000</v>
+        <v>84756000</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>63533000</v>
       </c>
       <c r="AV4" t="n">
-        <v>10488000</v>
+        <v>13121000</v>
       </c>
       <c r="AW4" t="n">
-        <v>7120000</v>
+        <v>8102000</v>
       </c>
       <c r="AX4" t="n">
-        <v>6756000</v>
+        <v>7530000</v>
       </c>
       <c r="AY4" t="n">
         <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1706502000</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>12261000</v>
-      </c>
+        <v>720013000</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
-        <v>1251957000</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>47886000</v>
+        <v>23273000</v>
       </c>
       <c r="BD4" t="n">
-        <v>159933000</v>
+        <v>256628000</v>
       </c>
       <c r="BE4" t="n">
-        <v>159933000</v>
+        <v>245455000</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>11173000</v>
       </c>
       <c r="BG4" t="n">
-        <v>27799000</v>
+        <v>98566000</v>
       </c>
       <c r="BH4" t="n">
-        <v>1249000</v>
+        <v>11281000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1007000</v>
+        <v>2303000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>216671000</v>
+        <v>327962000</v>
       </c>
       <c r="BK4" t="n">
-        <v>11012000</v>
+        <v>14242000</v>
       </c>
       <c r="BL4" t="n">
-        <v>205659000</v>
+        <v>313720000</v>
       </c>
       <c r="BM4" t="n">
-        <v>205659000</v>
+        <v>313720000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>412608000</v>
@@ -2154,46 +2160,46 @@
         <v>412608000</v>
       </c>
       <c r="D5" t="n">
-        <v>716013000</v>
+        <v>58837000</v>
       </c>
       <c r="E5" t="n">
-        <v>990905000</v>
+        <v>247521000</v>
       </c>
       <c r="F5" t="n">
-        <v>-730951000</v>
+        <v>524784000</v>
       </c>
       <c r="G5" t="n">
-        <v>1459511000</v>
+        <v>995738000</v>
       </c>
       <c r="H5" t="n">
-        <v>300621000</v>
+        <v>479274000</v>
       </c>
       <c r="I5" t="n">
-        <v>-730951000</v>
+        <v>524784000</v>
       </c>
       <c r="J5" t="n">
-        <v>2981000</v>
+        <v>2928000</v>
       </c>
       <c r="K5" t="n">
-        <v>471587000</v>
+        <v>751145000</v>
       </c>
       <c r="L5" t="n">
-        <v>1349511000</v>
+        <v>850614000</v>
       </c>
       <c r="M5" t="n">
-        <v>718076000</v>
+        <v>1078429000</v>
       </c>
       <c r="N5" t="n">
-        <v>246489000</v>
+        <v>327284000</v>
       </c>
       <c r="O5" t="n">
-        <v>471587000</v>
+        <v>751145000</v>
       </c>
       <c r="P5" t="n">
-        <v>32857000</v>
+        <v>5085000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-302889000</v>
+        <v>-18214000</v>
       </c>
       <c r="R5" t="n">
         <v>51487000</v>
@@ -2205,129 +2211,123 @@
         <v>3634000</v>
       </c>
       <c r="U5" t="n">
-        <v>1189941000</v>
+        <v>334380000</v>
       </c>
       <c r="V5" t="n">
-        <v>962812000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>83375000</v>
-      </c>
+        <v>100009000</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>879437000</v>
+        <v>100009000</v>
       </c>
       <c r="Y5" t="n">
-        <v>1513000</v>
+        <v>540000</v>
       </c>
       <c r="Z5" t="n">
-        <v>877924000</v>
+        <v>99469000</v>
       </c>
       <c r="AA5" t="n">
-        <v>227129000</v>
+        <v>234371000</v>
       </c>
       <c r="AB5" t="n">
-        <v>111468000</v>
+        <v>147512000</v>
       </c>
       <c r="AC5" t="n">
-        <v>1468000</v>
+        <v>2388000</v>
       </c>
       <c r="AD5" t="n">
-        <v>110000000</v>
+        <v>145124000</v>
       </c>
       <c r="AE5" t="n">
-        <v>81338000</v>
+        <v>74251000</v>
       </c>
       <c r="AF5" t="n">
-        <v>23947000</v>
+        <v>18739000</v>
       </c>
       <c r="AG5" t="n">
-        <v>15235000</v>
+        <v>6381000</v>
       </c>
       <c r="AH5" t="n">
-        <v>42156000</v>
+        <v>49131000</v>
       </c>
       <c r="AI5" t="n">
-        <v>1908017000</v>
+        <v>1412809000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1380267000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>-67196458.196013</v>
-      </c>
+        <v>699164000</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
-        <v>114015000</v>
+        <v>266000</v>
       </c>
       <c r="AN5" t="n">
-        <v>34065000</v>
+        <v>163579000</v>
       </c>
       <c r="AO5" t="n">
-        <v>34065000</v>
+        <v>163579000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1202538000</v>
+        <v>226361000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1202538000</v>
+        <v>226361000</v>
       </c>
       <c r="AR5" t="n">
-        <v>29649000</v>
+        <v>288310000</v>
       </c>
       <c r="AS5" t="n">
-        <v>-36896000</v>
+        <v>-11012000</v>
       </c>
       <c r="AT5" t="n">
-        <v>66545000</v>
-      </c>
-      <c r="AU5" t="inlineStr"/>
+        <v>299322000</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>279075000</v>
+      </c>
       <c r="AV5" t="n">
-        <v>55616000</v>
+        <v>11250000</v>
       </c>
       <c r="AW5" t="n">
-        <v>10929000</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>6582000</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
+        <v>8997000</v>
+      </c>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="n">
-        <v>527750000</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1342000</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
+        <v>713645000</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="n">
-        <v>114375000</v>
+        <v>48145000</v>
       </c>
       <c r="BD5" t="n">
-        <v>81763000</v>
+        <v>390608000</v>
       </c>
       <c r="BE5" t="n">
-        <v>81763000</v>
-      </c>
-      <c r="BF5" t="inlineStr"/>
+        <v>383541000</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>7067000</v>
+      </c>
       <c r="BG5" t="n">
-        <v>52290000</v>
-      </c>
-      <c r="BH5" t="inlineStr"/>
+        <v>43664000</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>40632000</v>
+      </c>
       <c r="BI5" t="n">
-        <v>6069000</v>
+        <v>4840000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>271911000</v>
+        <v>185756000</v>
       </c>
       <c r="BK5" t="inlineStr"/>
       <c r="BL5" t="n">
-        <v>271911000</v>
+        <v>185756000</v>
       </c>
       <c r="BM5" t="n">
-        <v>271911000</v>
+        <v>185756000</v>
       </c>
     </row>
   </sheetData>
@@ -2608,618 +2608,618 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-428075000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
+        <v>165660000</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>-51000000</v>
+        <v>-982168000</v>
       </c>
       <c r="E2" t="n">
-        <v>295593000</v>
+        <v>1052923000</v>
       </c>
       <c r="F2" t="n">
-        <v>-177557000</v>
+        <v>-31386000</v>
       </c>
       <c r="G2" t="n">
-        <v>185756000</v>
+        <v>271911000</v>
       </c>
       <c r="H2" t="n">
-        <v>313720000</v>
+        <v>207494000</v>
       </c>
       <c r="I2" t="n">
-        <v>-1361000</v>
+        <v>-179000</v>
       </c>
       <c r="J2" t="n">
-        <v>-126603000</v>
+        <v>64596000</v>
       </c>
       <c r="K2" t="n">
-        <v>217459000</v>
+        <v>12280000</v>
       </c>
       <c r="L2" t="n">
-        <v>25866000</v>
+        <v>16900000</v>
       </c>
       <c r="M2" t="n">
-        <v>-179000</v>
+        <v>-114000</v>
       </c>
       <c r="N2" t="n">
-        <v>-45574000</v>
+        <v>-20311000</v>
       </c>
       <c r="O2" t="n">
-        <v>-45574000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
+        <v>-20311000</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>244593000</v>
+        <v>70755000</v>
       </c>
       <c r="S2" t="n">
-        <v>244593000</v>
+        <v>70755000</v>
       </c>
       <c r="T2" t="n">
-        <v>-51000000</v>
+        <v>-982168000</v>
       </c>
       <c r="U2" t="n">
-        <v>295593000</v>
+        <v>1052923000</v>
       </c>
       <c r="V2" t="n">
-        <v>-93544000</v>
+        <v>-144730000</v>
       </c>
       <c r="W2" t="n">
-        <v>2746000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>8400000</v>
-      </c>
+        <v>3561000</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
-        <v>13800000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>13800000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>67067000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>77698000</v>
-      </c>
+        <v>-132000000</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
-        <v>-10631000</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
+        <v>-132000000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-5717000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-5717000</v>
+      </c>
       <c r="AH2" t="n">
-        <v>-177557000</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
+        <v>-25669000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
       <c r="AJ2" t="n">
-        <v>-177557000</v>
+        <v>-25669000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-250518000</v>
+        <v>197046000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-4834000</v>
+        <v>-49275000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-268726000</v>
+        <v>-75716000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-64946000</v>
+        <v>19760000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-42680000</v>
+        <v>13408000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1528000</v>
+        <v>-4909000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-133980000</v>
+        <v>-2235000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-25592000</v>
+        <v>-101740000</v>
       </c>
       <c r="AS2" t="n">
-        <v>2601000</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
+        <v>45746000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>34774000</v>
+      </c>
       <c r="AU2" t="n">
-        <v>39888000</v>
+        <v>64025000</v>
       </c>
       <c r="AV2" t="n">
-        <v>31063000</v>
+        <v>57787000</v>
       </c>
       <c r="AW2" t="n">
-        <v>8825000</v>
+        <v>6238000</v>
       </c>
       <c r="AX2" t="n">
-        <v>2715000</v>
+        <v>-2064000</v>
       </c>
       <c r="AY2" t="n">
-        <v>12000</v>
+        <v>160000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-427000</v>
+        <v>320000</v>
       </c>
       <c r="BA2" t="n">
-        <v>-9221000</v>
+        <v>193248000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>13882000</v>
+        <v>170335000</v>
       </c>
       <c r="C3" t="n">
-        <v>-91091000</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-100000000</v>
+        <v>-160000000</v>
       </c>
       <c r="E3" t="n">
-        <v>50000000</v>
+        <v>100000000</v>
       </c>
       <c r="F3" t="n">
-        <v>-49684000</v>
+        <v>-28363000</v>
       </c>
       <c r="G3" t="n">
-        <v>313720000</v>
+        <v>260074000</v>
       </c>
       <c r="H3" t="n">
-        <v>260074000</v>
+        <v>271911000</v>
       </c>
       <c r="I3" t="n">
-        <v>759000</v>
+        <v>501000</v>
       </c>
       <c r="J3" t="n">
-        <v>52887000</v>
+        <v>-12338000</v>
       </c>
       <c r="K3" t="n">
-        <v>-157156000</v>
+        <v>-94417000</v>
       </c>
       <c r="L3" t="n">
-        <v>92536000</v>
+        <v>11901000</v>
       </c>
       <c r="M3" t="n">
-        <v>-46000</v>
-      </c>
-      <c r="N3" t="n">
-        <v>-43767000</v>
-      </c>
+        <v>-117000</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>-43767000</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-91091000</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-91091000</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>-50000000</v>
+        <v>-60000000</v>
       </c>
       <c r="S3" t="n">
-        <v>-50000000</v>
+        <v>-60000000</v>
       </c>
       <c r="T3" t="n">
-        <v>-100000000</v>
+        <v>-160000000</v>
       </c>
       <c r="U3" t="n">
-        <v>50000000</v>
+        <v>100000000</v>
       </c>
       <c r="V3" t="n">
-        <v>146477000</v>
+        <v>-116619000</v>
       </c>
       <c r="W3" t="n">
-        <v>4137000</v>
+        <v>3032000</v>
       </c>
       <c r="X3" t="n">
-        <v>5034000</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-3000000</v>
+        <v>-10800000</v>
       </c>
       <c r="Z3" t="n">
-        <v>10800000</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-13800000</v>
+        <v>-10800000</v>
       </c>
       <c r="AB3" t="n">
-        <v>197990000</v>
+        <v>-87288000</v>
       </c>
       <c r="AC3" t="n">
-        <v>372290000</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-174300000</v>
+        <v>-87288000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>-18294000</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>-18294000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-49684000</v>
+        <v>3931000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>14000000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-49684000</v>
+        <v>-10069000</v>
       </c>
       <c r="AK3" t="n">
-        <v>63566000</v>
+        <v>198698000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-37336000</v>
+        <v>-35972000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-45389000</v>
+        <v>7921000</v>
       </c>
       <c r="AN3" t="n">
-        <v>39618000</v>
+        <v>12629000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-5616000</v>
+        <v>1429000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1501000</v>
+        <v>779000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-96695000</v>
+        <v>-78170000</v>
       </c>
       <c r="AR3" t="n">
-        <v>18805000</v>
+        <v>71254000</v>
       </c>
       <c r="AS3" t="n">
-        <v>15166000</v>
+        <v>41640000</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1296000</v>
       </c>
       <c r="AU3" t="n">
-        <v>38972000</v>
+        <v>64066000</v>
       </c>
       <c r="AV3" t="n">
-        <v>34894000</v>
+        <v>57258000</v>
       </c>
       <c r="AW3" t="n">
-        <v>4078000</v>
+        <v>6808000</v>
       </c>
       <c r="AX3" t="n">
-        <v>514000</v>
+        <v>4021000</v>
       </c>
       <c r="AY3" t="n">
-        <v>23000</v>
+        <v>432000</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>91842000</v>
+        <v>119495000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>170335000</v>
+        <v>13882000</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-91091000</v>
       </c>
       <c r="D4" t="n">
-        <v>-160000000</v>
+        <v>-100000000</v>
       </c>
       <c r="E4" t="n">
-        <v>100000000</v>
+        <v>50000000</v>
       </c>
       <c r="F4" t="n">
-        <v>-28363000</v>
+        <v>-49684000</v>
       </c>
       <c r="G4" t="n">
+        <v>313720000</v>
+      </c>
+      <c r="H4" t="n">
         <v>260074000</v>
       </c>
-      <c r="H4" t="n">
-        <v>271911000</v>
-      </c>
       <c r="I4" t="n">
-        <v>501000</v>
+        <v>759000</v>
       </c>
       <c r="J4" t="n">
-        <v>-12338000</v>
+        <v>52887000</v>
       </c>
       <c r="K4" t="n">
-        <v>-94417000</v>
+        <v>-157156000</v>
       </c>
       <c r="L4" t="n">
-        <v>11901000</v>
+        <v>92536000</v>
       </c>
       <c r="M4" t="n">
-        <v>-117000</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
+        <v>-46000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-43767000</v>
+      </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-43767000</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-91091000</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-91091000</v>
       </c>
       <c r="R4" t="n">
-        <v>-60000000</v>
+        <v>-50000000</v>
       </c>
       <c r="S4" t="n">
-        <v>-60000000</v>
+        <v>-50000000</v>
       </c>
       <c r="T4" t="n">
-        <v>-160000000</v>
+        <v>-100000000</v>
       </c>
       <c r="U4" t="n">
-        <v>100000000</v>
+        <v>50000000</v>
       </c>
       <c r="V4" t="n">
-        <v>-116619000</v>
+        <v>146477000</v>
       </c>
       <c r="W4" t="n">
-        <v>3032000</v>
+        <v>4137000</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>5034000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-10800000</v>
+        <v>-3000000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>10800000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-10800000</v>
+        <v>-13800000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-87288000</v>
+        <v>197990000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>372290000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-87288000</v>
+        <v>-174300000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-18294000</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>-18294000</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>3931000</v>
+        <v>-49684000</v>
       </c>
       <c r="AI4" t="n">
-        <v>14000000</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-10069000</v>
+        <v>-49684000</v>
       </c>
       <c r="AK4" t="n">
-        <v>198698000</v>
+        <v>63566000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-35972000</v>
+        <v>-37336000</v>
       </c>
       <c r="AM4" t="n">
-        <v>7921000</v>
+        <v>-45389000</v>
       </c>
       <c r="AN4" t="n">
-        <v>12629000</v>
+        <v>39618000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1429000</v>
+        <v>-5616000</v>
       </c>
       <c r="AP4" t="n">
-        <v>779000</v>
+        <v>-1501000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-78170000</v>
+        <v>-96695000</v>
       </c>
       <c r="AR4" t="n">
-        <v>71254000</v>
+        <v>18805000</v>
       </c>
       <c r="AS4" t="n">
-        <v>41640000</v>
+        <v>15166000</v>
       </c>
       <c r="AT4" t="n">
-        <v>1296000</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>64066000</v>
+        <v>38972000</v>
       </c>
       <c r="AV4" t="n">
-        <v>57258000</v>
+        <v>34894000</v>
       </c>
       <c r="AW4" t="n">
-        <v>6808000</v>
+        <v>4078000</v>
       </c>
       <c r="AX4" t="n">
-        <v>4021000</v>
+        <v>514000</v>
       </c>
       <c r="AY4" t="n">
-        <v>432000</v>
+        <v>23000</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>119495000</v>
+        <v>91842000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>165660000</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>-428075000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
       <c r="D5" t="n">
-        <v>-982168000</v>
+        <v>-51000000</v>
       </c>
       <c r="E5" t="n">
-        <v>1052923000</v>
+        <v>295593000</v>
       </c>
       <c r="F5" t="n">
-        <v>-31386000</v>
+        <v>-177557000</v>
       </c>
       <c r="G5" t="n">
-        <v>271911000</v>
+        <v>185756000</v>
       </c>
       <c r="H5" t="n">
-        <v>207494000</v>
+        <v>313720000</v>
       </c>
       <c r="I5" t="n">
+        <v>-1361000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-126603000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>217459000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>25866000</v>
+      </c>
+      <c r="M5" t="n">
         <v>-179000</v>
       </c>
-      <c r="J5" t="n">
-        <v>64596000</v>
-      </c>
-      <c r="K5" t="n">
-        <v>12280000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>16900000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>-114000</v>
-      </c>
       <c r="N5" t="n">
-        <v>-20311000</v>
+        <v>-45574000</v>
       </c>
       <c r="O5" t="n">
-        <v>-20311000</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+        <v>-45574000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
       <c r="R5" t="n">
-        <v>70755000</v>
+        <v>244593000</v>
       </c>
       <c r="S5" t="n">
-        <v>70755000</v>
+        <v>244593000</v>
       </c>
       <c r="T5" t="n">
-        <v>-982168000</v>
+        <v>-51000000</v>
       </c>
       <c r="U5" t="n">
-        <v>1052923000</v>
+        <v>295593000</v>
       </c>
       <c r="V5" t="n">
-        <v>-144730000</v>
+        <v>-93544000</v>
       </c>
       <c r="W5" t="n">
-        <v>3561000</v>
-      </c>
-      <c r="X5" t="inlineStr"/>
+        <v>2746000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>8400000</v>
+      </c>
       <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="inlineStr"/>
+        <v>13800000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>13800000</v>
+      </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-132000000</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>67067000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>77698000</v>
+      </c>
       <c r="AD5" t="n">
-        <v>-132000000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-5717000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-5717000</v>
-      </c>
+        <v>-10631000</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>-25669000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
+        <v>-177557000</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>-25669000</v>
+        <v>-177557000</v>
       </c>
       <c r="AK5" t="n">
-        <v>197046000</v>
+        <v>-250518000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-49275000</v>
+        <v>-4834000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-75716000</v>
+        <v>-268726000</v>
       </c>
       <c r="AN5" t="n">
-        <v>19760000</v>
+        <v>-64946000</v>
       </c>
       <c r="AO5" t="n">
-        <v>13408000</v>
+        <v>-42680000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-4909000</v>
+        <v>-1528000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-2235000</v>
+        <v>-133980000</v>
       </c>
       <c r="AR5" t="n">
-        <v>-101740000</v>
+        <v>-25592000</v>
       </c>
       <c r="AS5" t="n">
-        <v>45746000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>34774000</v>
-      </c>
+        <v>2601000</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="n">
-        <v>64025000</v>
+        <v>39888000</v>
       </c>
       <c r="AV5" t="n">
-        <v>57787000</v>
+        <v>31063000</v>
       </c>
       <c r="AW5" t="n">
-        <v>6238000</v>
+        <v>8825000</v>
       </c>
       <c r="AX5" t="n">
-        <v>-2064000</v>
+        <v>2715000</v>
       </c>
       <c r="AY5" t="n">
-        <v>160000</v>
+        <v>12000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>320000</v>
+        <v>-427000</v>
       </c>
       <c r="BA5" t="n">
-        <v>193248000</v>
+        <v>-9221000</v>
       </c>
     </row>
   </sheetData>
@@ -3749,187 +3749,187 @@
       </c>
       <c r="CY1" t="inlineStr">
         <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
         </is>
       </c>
       <c r="EJ1" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Yeung Nam  Chan', 'age': 70, 'title': 'Executive Chairman', 'yearBorn': 1955, 'fiscalYear': 2025, 'totalPay': 1112104, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jie Pin  Fu', 'age': 58, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1967, 'fiscalYear': 2025, 'totalPay': 763413, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Bao Hua  Liu', 'age': 48, 'title': 'Executive Director', 'yearBorn': 1977, 'fiscalYear': 2025, 'totalPay': 572270, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Tinghui  Zhang', 'age': 46, 'title': 'Executive Director', 'yearBorn': 1979, 'fiscalYear': 2025, 'totalPay': 117003, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ka Man  Sin FCCA, HKICPA', 'age': 57, 'title': 'Company Secretary', 'yearBorn': 1968, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Yeung Nam  Chan', 'age': 70, 'title': 'Executive Chairman', 'yearBorn': 1955, 'fiscalYear': 2025, 'totalPay': 1111217, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jie Pin  Fu', 'age': 58, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1967, 'fiscalYear': 2025, 'totalPay': 762804, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Bao Hua  Liu', 'age': 48, 'title': 'Executive Director', 'yearBorn': 1977, 'fiscalYear': 2025, 'totalPay': 571814, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Tinghui  Zhang', 'age': 46, 'title': 'Executive Director', 'yearBorn': 1979, 'fiscalYear': 2025, 'totalPay': 116909, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ka Man  Sin FCCA, HKICPA', 'age': 57, 'title': 'Company Secretary', 'yearBorn': 1968, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -4032,28 +4032,28 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V2" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W2" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="X2" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="AC2" t="n">
         <v>1720742400</v>
@@ -4062,29 +4062,29 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.644</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="AF2" t="n">
-        <v>80000</v>
+        <v>50000</v>
       </c>
       <c r="AG2" t="n">
-        <v>80000</v>
+        <v>50000</v>
       </c>
       <c r="AH2" t="n">
-        <v>346560</v>
+        <v>267959</v>
       </c>
       <c r="AI2" t="n">
-        <v>215200</v>
+        <v>146000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>215200</v>
+        <v>146000</v>
       </c>
       <c r="AK2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL2" t="n">
         <v>1.35</v>
       </c>
-      <c r="AL2" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
@@ -4092,13 +4092,13 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>678395520</v>
+        <v>626573632</v>
       </c>
       <c r="AP2" t="n">
-        <v>678395520</v>
+        <v>626573640</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.385</v>
+        <v>0.405</v>
       </c>
       <c r="AR2" t="n">
         <v>2.04</v>
@@ -4110,13 +4110,13 @@
         <v>0.34</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.831464</v>
+        <v>4.4623938</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.6254</v>
+        <v>1.5534</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.2999</v>
+        <v>1.32135</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
@@ -4133,7 +4133,7 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1086545536</v>
+        <v>1041158656</v>
       </c>
       <c r="BC2" t="n">
         <v>-0.25741</v>
@@ -4154,10 +4154,10 @@
         <v>471108000</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.0047433</v>
+        <v>2.0036795</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.71829647</v>
+        <v>0.66377884</v>
       </c>
       <c r="BK2" t="n">
         <v>1767139200</v>
@@ -4175,16 +4175,16 @@
         <v>-0.1</v>
       </c>
       <c r="BP2" t="n">
-        <v>7.738</v>
+        <v>7.415</v>
       </c>
       <c r="BQ2" t="n">
-        <v>146.95</v>
+        <v>140.811</v>
       </c>
       <c r="BR2" t="n">
-        <v>2.6923077</v>
+        <v>2.2470589</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BT2" t="n">
         <v>0.121</v>
@@ -4198,7 +4198,7 @@
         </is>
       </c>
       <c r="BW2" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
@@ -4297,140 +4297,140 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
+      <c r="CY2" t="n">
+        <v>-3.623185</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.44</v>
+        <v>-0.049999952</v>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
+          <t>1.31 - 1.38</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DD2" t="n">
+        <v>267959</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0.9250001</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>2.2839508</v>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>0.405 - 2.04</t>
+        </is>
+      </c>
+      <c r="DH2" t="n">
+        <v>-0.7099999</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>-0.34803918</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>224.70589</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>1743083061</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>1743083061</v>
+      </c>
+      <c r="DM2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>-0.2234</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>-0.14381357</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0.0086500645</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>0.006546384</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>HUAYUEXPRESSWAY</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>Huayu Expressway Group Limited</t>
+        </is>
+      </c>
+      <c r="DW2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DY2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>1261531800000</v>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="EB2" t="n">
+        <v>1782113983</v>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="DC2" t="inlineStr">
+      <c r="ED2" t="inlineStr">
         <is>
           <t>finmb_82843771</t>
         </is>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="EE2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="EF2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>1261531800000</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>1.44 - 1.49</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DK2" t="n">
-        <v>346560</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>1.0550001</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>2.74026</v>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>0.385 - 2.04</t>
-        </is>
-      </c>
-      <c r="DO2" t="n">
-        <v>-0.5999999</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>-0.2941176</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>269.23077</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>1743083061</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>1743083061</v>
-      </c>
-      <c r="DT2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>-0.18539989</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>-0.114064164</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>0.1401</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>0.10777752</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EB2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EC2" t="n">
+      <c r="EG2" t="n">
         <v>28800000</v>
       </c>
-      <c r="ED2" t="inlineStr">
+      <c r="EH2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="EE2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>HUAYUEXPRESSWAY</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>Huayu Expressway Group Limited</t>
-        </is>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EI2" t="n">
-        <v>1780384655</v>
+      <c r="EI2" t="b">
+        <v>0</v>
       </c>
       <c r="EJ2" t="inlineStr"/>
     </row>
